--- a/artfynd/A 36690-2025 artfynd.xlsx
+++ b/artfynd/A 36690-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>63912111</v>
       </c>
       <c r="B2" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106190</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>427172.5785570776</v>
+        <v>427173</v>
       </c>
       <c r="R2" t="n">
-        <v>6231694.216952779</v>
+        <v>6231694</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -748,19 +743,9 @@
           <t>2000-09-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2000-09-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 36690-2025 artfynd.xlsx
+++ b/artfynd/A 36690-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63912111</v>
       </c>
       <c r="B2" t="n">
-        <v>106190</v>
+        <v>106202</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36690-2025 artfynd.xlsx
+++ b/artfynd/A 36690-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63912111</v>
       </c>
       <c r="B2" t="n">
-        <v>106202</v>
+        <v>106211</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36690-2025 artfynd.xlsx
+++ b/artfynd/A 36690-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63912111</v>
       </c>
       <c r="B2" t="n">
-        <v>106211</v>
+        <v>106216</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36690-2025 artfynd.xlsx
+++ b/artfynd/A 36690-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63912111</v>
       </c>
       <c r="B2" t="n">
-        <v>106216</v>
+        <v>106244</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36690-2025 artfynd.xlsx
+++ b/artfynd/A 36690-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63912111</v>
       </c>
       <c r="B2" t="n">
-        <v>106244</v>
+        <v>106250</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36690-2025 artfynd.xlsx
+++ b/artfynd/A 36690-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63912111</v>
       </c>
       <c r="B2" t="n">
-        <v>106250</v>
+        <v>106257</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36690-2025 artfynd.xlsx
+++ b/artfynd/A 36690-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63912111</v>
       </c>
       <c r="B2" t="n">
-        <v>106257</v>
+        <v>106261</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36690-2025 artfynd.xlsx
+++ b/artfynd/A 36690-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63912111</v>
       </c>
       <c r="B2" t="n">
-        <v>106261</v>
+        <v>106268</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36690-2025 artfynd.xlsx
+++ b/artfynd/A 36690-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63912111</v>
       </c>
       <c r="B2" t="n">
-        <v>106271</v>
+        <v>106276</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36690-2025 artfynd.xlsx
+++ b/artfynd/A 36690-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63912111</v>
       </c>
       <c r="B2" t="n">
-        <v>106276</v>
+        <v>106284</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36690-2025 artfynd.xlsx
+++ b/artfynd/A 36690-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63912111</v>
       </c>
       <c r="B2" t="n">
-        <v>106284</v>
+        <v>106294</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
